--- a/analysis/cocoblu-supply-2026-09-04/Cocoblu_Supply_Plan_v5_ISK3.xlsx
+++ b/analysis/cocoblu-supply-2026-09-04/Cocoblu_Supply_Plan_v5_ISK3.xlsx
@@ -19,11 +19,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0_Summary'!$A$1:$B$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Dispatch by PO'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_Dispatch lines'!$A$1:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_Dispatch lines'!$A$1:$N$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_SKU plan 35d'!$A$1:$S$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_Franchise cap'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5_Ask Amazon for PO'!$A$1:$K$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_Hold or cancel'!$A$1:$L$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_Hold or cancel'!$A$1:$L$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'7_EOL - cancel these'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4129</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="8">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7295316</v>
+        <v>6833367</v>
       </c>
     </row>
     <row r="9">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8666</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="10">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>452</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15">
@@ -610,7 +610,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Click 20000, Quad Pro 1.5m 60W</t>
+          <t>Click 20000, Quad Pro 1.5m 60W, Zeno 65W retractable</t>
         </is>
       </c>
     </row>
@@ -721,10 +721,10 @@
         <v>46285</v>
       </c>
       <c r="E2" t="n">
-        <v>2106</v>
+        <v>1822</v>
       </c>
       <c r="F2" t="n">
-        <v>4157837</v>
+        <v>3695888</v>
       </c>
     </row>
     <row r="3">
@@ -827,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1191,50 +1191,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0G4VHN9CZ</t>
+          <t>B0FWQYNB6P</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WCZENO65WWHT</t>
+          <t>WCJTPRO70WSIL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Zeno 65W GaN Type C Fast Charger Retractable Cable 68cm PD PPS iPhone Pixel Supports </t>
+          <t>Stuffcool Jetset Pro Smallest 70W GaN International Travel Adapter with 4 USB Ports EU UK USA A</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1626.58</v>
+        <v>1789.29</v>
       </c>
       <c r="G7" t="n">
-        <v>284</v>
+        <v>135</v>
       </c>
       <c r="H7" t="n">
-        <v>284</v>
+        <v>135</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>46285</v>
+        <v>46294</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>46289</v>
+        <v>46298</v>
       </c>
       <c r="M7" t="n">
-        <v>461949</v>
+        <v>241554</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1245,50 +1245,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0FWQYNB6P</t>
+          <t>B0FSRCKNCW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WCJTPRO70WSIL</t>
+          <t>PBNEMOSIL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuffcool Jetset Pro Smallest 70W GaN International Travel Adapter with 4 USB Ports EU UK USA A</t>
+          <t xml:space="preserve">Stuffcool Nemo 10000mAh Compact Magnetic Wireless Charging Power Bank up to 15W for iPhone 20W </t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1789.29</v>
+        <v>1524.81</v>
       </c>
       <c r="G8" t="n">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="H8" t="n">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>46266</v>
+        <v>46244</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>46294</v>
+        <v>46285</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
       <c r="M8" t="n">
-        <v>241554</v>
+        <v>50319</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1307,30 +1307,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0FSRCKNCW</t>
+          <t>B0DMDZF5SV</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PBNEMOSIL</t>
+          <t>PBGIGAGRY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Nemo 10000mAh Compact Magnetic Wireless Charging Power Bank up to 15W for iPhone 20W </t>
+          <t>Stuffcool GIGA Smallest 65W 20000mAh Laptop Powerbank with Built in 100W 5A Type C Cable,Charge</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1524.81</v>
+        <v>2474.95</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>642</v>
       </c>
       <c r="H9" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>46244</v>
@@ -1342,11 +1342,11 @@
         <v>46289</v>
       </c>
       <c r="M9" t="n">
-        <v>50319</v>
+        <v>225220</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>P0b-New arrival, never sold</t>
+          <t>P1-Incumbent (running down)</t>
         </is>
       </c>
     </row>
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DMDZF5SV</t>
+          <t>B0DFZ3FK9F</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PBGIGAGRY</t>
+          <t>PBCLICK10TNM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stuffcool GIGA Smallest 65W 20000mAh Laptop Powerbank with Built in 100W 5A Type C Cable,Charge</t>
+          <t>Stuffcool Click 10000mAh Slim Magnetic Wireless Powerbank Natural Titanium Finish Perfect for i</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2474.95</v>
+        <v>1185.85</v>
       </c>
       <c r="G10" t="n">
-        <v>642</v>
+        <v>758</v>
       </c>
       <c r="H10" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="I10" t="n">
-        <v>551</v>
+        <v>714</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>46244</v>
@@ -1396,7 +1396,7 @@
         <v>46289</v>
       </c>
       <c r="M10" t="n">
-        <v>225220</v>
+        <v>52177</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1415,30 +1415,30 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DFZ3FK9F</t>
+          <t>B0DZHKBBM1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PBCLICK10TNM</t>
+          <t>PBMAVERICKBLK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stuffcool Click 10000mAh Slim Magnetic Wireless Powerbank Natural Titanium Finish Perfect for i</t>
+          <t xml:space="preserve">Stuffcool Maverick Mini 20,000mAh Powerbank with 20W Built-in Lightning &amp; Type-C Cables, 22.5W </t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1185.85</v>
+        <v>1219.73</v>
       </c>
       <c r="G11" t="n">
-        <v>758</v>
+        <v>504</v>
       </c>
       <c r="H11" t="n">
-        <v>44</v>
+        <v>504</v>
       </c>
       <c r="I11" t="n">
-        <v>714</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>46244</v>
@@ -1450,61 +1450,61 @@
         <v>46289</v>
       </c>
       <c r="M11" t="n">
-        <v>52177</v>
+        <v>614744</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>P1-Incumbent (running down)</t>
+          <t>P2-Critical</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DZHKBBM1</t>
+          <t>B0DFYZTJMC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PBMAVERICKBLK</t>
+          <t>PBROAM10WHT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Maverick Mini 20,000mAh Powerbank with 20W Built-in Lightning &amp; Type-C Cables, 22.5W </t>
+          <t xml:space="preserve">Stuffcool Roam 10000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins </t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1219.73</v>
+        <v>889.24</v>
       </c>
       <c r="G12" t="n">
-        <v>504</v>
+        <v>121</v>
       </c>
       <c r="H12" t="n">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M12" t="n">
-        <v>614744</v>
+        <v>66693</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1515,50 +1515,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DFYZTJMC</t>
+          <t>B0DZHKBBM1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PBROAM10WHT</t>
+          <t>PBMAVERICKBLK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Roam 10000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins </t>
+          <t xml:space="preserve">Stuffcool Maverick Mini 20,000mAh Powerbank with 20W Built-in Lightning &amp; Type-C Cables, 22.5W </t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>889.24</v>
+        <v>1219.73</v>
       </c>
       <c r="G13" t="n">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="H13" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="I13" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>46258</v>
+        <v>46266</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
       <c r="M13" t="n">
-        <v>66693</v>
+        <v>65865</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1569,11 +1569,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1594,25 +1594,25 @@
         <v>1219.73</v>
       </c>
       <c r="G14" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H14" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>46298</v>
+        <v>46290</v>
       </c>
       <c r="M14" t="n">
-        <v>65865</v>
+        <v>58547</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1623,50 +1623,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DZHKBBM1</t>
+          <t>B0FT2VNW5H</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PBMAVERICKBLK</t>
+          <t>WCZENO30WWHT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Maverick Mini 20,000mAh Powerbank with 20W Built-in Lightning &amp; Type-C Cables, 22.5W </t>
+          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cable 75cm PD PPS iPhone Pixel Samsung S</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1219.73</v>
+        <v>1084.2</v>
       </c>
       <c r="G15" t="n">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>46258</v>
+        <v>46266</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
       <c r="M15" t="n">
-        <v>58547</v>
+        <v>47705</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1677,50 +1677,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0FT2VNW5H</t>
+          <t>B0FSSCW7WZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WCZENO30WWHT</t>
+          <t>DUPLOBLK</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cable 75cm PD PPS iPhone Pixel Samsung S</t>
+          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1084.2</v>
+        <v>698.6900000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="H16" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I16" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>46266</v>
+        <v>46244</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46294</v>
+        <v>46285</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
       <c r="M16" t="n">
-        <v>47705</v>
+        <v>24454</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1731,50 +1731,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0FSSCW7WZ</t>
+          <t>B0H6J3YQ1D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DUPLOBLK</t>
+          <t>WCNVS25CBLU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone Blue</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>698.6900000000001</v>
+        <v>433.36</v>
       </c>
       <c r="G17" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M17" t="n">
-        <v>24454</v>
+        <v>4767</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1810,25 +1810,25 @@
         <v>433.36</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="M18" t="n">
-        <v>4767</v>
+        <v>3467</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1839,54 +1839,54 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0H6J3YQ1D</t>
+          <t>B0FL2H8HZ6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WCNVS25CBLU</t>
+          <t>PBGIGAMAXGRY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone Blue</t>
+          <t>Stuffcool Giga Max Smallest 25000mAh 100W Power Bank, Built-in Type-C Cable, Charges MacBook Pr</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>433.36</v>
+        <v>3284.1</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>2099</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>490</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1609</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46279</v>
+        <v>46285</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="M19" t="n">
-        <v>3467</v>
+        <v>1609209</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>P2-Critical</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
     </row>
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0FL2H8HZ6</t>
+          <t>B0D5JKBJTQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PBGIGAMAXGRY</t>
+          <t>PBMAJORULTRASIL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stuffcool Giga Max Smallest 25000mAh 100W Power Bank, Built-in Type-C Cable, Charges MacBook Pr</t>
+          <t>Stuffcool Major Ultra 65W PD Super Fast USB Charging 20000Mah Laptop Powerbank Supports Super F</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3284.1</v>
+        <v>1601.1</v>
       </c>
       <c r="G20" t="n">
-        <v>2099</v>
+        <v>334</v>
       </c>
       <c r="H20" t="n">
-        <v>490</v>
+        <v>334</v>
       </c>
       <c r="I20" t="n">
-        <v>1609</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>46244</v>
@@ -1936,7 +1936,7 @@
         <v>46289</v>
       </c>
       <c r="M20" t="n">
-        <v>1609209</v>
+        <v>534767</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1955,30 +1955,30 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0D5JKBJTQ</t>
+          <t>B0FHWN3M23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PBMAJORULTRASIL</t>
+          <t>PBODINSIL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stuffcool Major Ultra 65W PD Super Fast USB Charging 20000Mah Laptop Powerbank Supports Super F</t>
+          <t xml:space="preserve">Stuffcool Odin 10000mAh Qi2 MagSafe Powerbank with 15W Wireless Charging, 35W PD Wired Output, </t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1601.1</v>
+        <v>2382.42</v>
       </c>
       <c r="G21" t="n">
-        <v>334</v>
+        <v>527</v>
       </c>
       <c r="H21" t="n">
-        <v>334</v>
+        <v>201</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>46244</v>
@@ -1990,7 +1990,7 @@
         <v>46289</v>
       </c>
       <c r="M21" t="n">
-        <v>534767</v>
+        <v>478866</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2001,50 +2001,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0FHWN3M23</t>
+          <t>B0D5JKBJTQ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PBODINSIL</t>
+          <t>PBMAJORULTRASIL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Odin 10000mAh Qi2 MagSafe Powerbank with 15W Wireless Charging, 35W PD Wired Output, </t>
+          <t>Stuffcool Major Ultra 65W PD Super Fast USB Charging 20000Mah Laptop Powerbank Supports Super F</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2382.42</v>
+        <v>1601.1</v>
       </c>
       <c r="G22" t="n">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="H22" t="n">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="I22" t="n">
-        <v>326</v>
+        <v>391</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M22" t="n">
-        <v>478866</v>
+        <v>185728</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2055,50 +2055,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0D5JKBJTQ</t>
+          <t>B0FY37VTSK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PBMAJORULTRASIL</t>
+          <t>WCNMDPROSIL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stuffcool Major Ultra 65W PD Super Fast USB Charging 20000Mah Laptop Powerbank Supports Super F</t>
+          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TFT Display,Super Fast Charging 2.0 Cha</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1601.1</v>
+        <v>3253.69</v>
       </c>
       <c r="G23" t="n">
-        <v>507</v>
+        <v>54</v>
       </c>
       <c r="H23" t="n">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="I23" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="M23" t="n">
-        <v>185728</v>
+        <v>175699</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2109,50 +2109,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0FY37VTSK</t>
+          <t>B0GR982Q8W</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>WCNMDPROSIL</t>
+          <t>WCNUMEN65WHT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TFT Display,Super Fast Charging 2.0 Cha</t>
+          <t>Stuffcool Numen 65, Smallest 65W GaN Charger with Dual USB-C PD PPS &amp; USB-A, SFC 2.0 &amp; 3.0, AVS</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3253.69</v>
+        <v>1138.44</v>
       </c>
       <c r="G24" t="n">
-        <v>54</v>
+        <v>285</v>
       </c>
       <c r="H24" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="M24" t="n">
-        <v>175699</v>
+        <v>112706</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2163,50 +2163,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0GR982Q8W</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WCNUMEN65WHT</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stuffcool Numen 65, Smallest 65W GaN Charger with Dual USB-C PD PPS &amp; USB-A, SFC 2.0 &amp; 3.0, AVS</t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1138.44</v>
+        <v>2168.95</v>
       </c>
       <c r="G25" t="n">
-        <v>285</v>
+        <v>40</v>
       </c>
       <c r="H25" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="I25" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="M25" t="n">
-        <v>112706</v>
+        <v>86758</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2217,50 +2217,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0FY37VTSK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>WCNMDPROSIL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TFT Display,Super Fast Charging 2.0 Cha</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2168.95</v>
+        <v>3253.69</v>
       </c>
       <c r="G26" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H26" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="M26" t="n">
-        <v>86758</v>
+        <v>81342</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2271,50 +2271,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0FY37VTSK</t>
+          <t>B0FWSNDJ2V</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WCNMDPROSIL</t>
+          <t>WCNMDIIWHT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TFT Display,Super Fast Charging 2.0 Cha</t>
+          <t>Stuffcool Nomad II Smallest 100W GaN Charger PD PPS Supports SFC 2.0 Charges MacBook, Laptop, S</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3253.69</v>
+        <v>2168.95</v>
       </c>
       <c r="G27" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="H27" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I27" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>46258</v>
+        <v>46266</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
       <c r="M27" t="n">
-        <v>81342</v>
+        <v>69406</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2325,50 +2325,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0FWSNDJ2V</t>
+          <t>B0H6Q2YQ9C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>WCNMDIIWHT</t>
+          <t>PBOMNIPROSIL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stuffcool Nomad II Smallest 100W GaN Charger PD PPS Supports SFC 2.0 Charges MacBook, Laptop, S</t>
+          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 10000mAh with Apple Watch Charger, 35W</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2168.95</v>
+        <v>3134.97</v>
       </c>
       <c r="G28" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H28" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>46298</v>
+        <v>46290</v>
       </c>
       <c r="M28" t="n">
-        <v>69406</v>
+        <v>56429</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2379,50 +2379,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0H6Q2YQ9C</t>
+          <t>B0FY37VTSK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PBOMNIPROSIL</t>
+          <t>WCNMDPROSIL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 10000mAh with Apple Watch Charger, 35W</t>
+          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TFT Display,Super Fast Charging 2.0 Cha</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3134.97</v>
+        <v>3253.69</v>
       </c>
       <c r="G29" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="M29" t="n">
-        <v>56429</v>
+        <v>52059</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0FY37VTSK</t>
+          <t>B0D8443PTW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WCNMDPROSIL</t>
+          <t>QUADPROMAXBLK</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TFT Display,Super Fast Charging 2.0 Cha</t>
+          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240W Rugged e-Marker chip gold plated co</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3253.69</v>
+        <v>508.05</v>
       </c>
       <c r="G30" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="H30" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>46244</v>
@@ -2476,7 +2476,7 @@
         <v>46289</v>
       </c>
       <c r="M30" t="n">
-        <v>52059</v>
+        <v>30483</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2487,50 +2487,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0D8443PTW</t>
+          <t>B0H5HYK4KZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>QUADPROMAXBLK</t>
+          <t>PBOMNIIVRY</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240W Rugged e-Marker chip gold plated co</t>
+          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>508.05</v>
+        <v>1692.59</v>
       </c>
       <c r="G31" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="H31" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M31" t="n">
-        <v>30483</v>
+        <v>20311</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2541,50 +2541,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0H5HYK4KZ</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PBOMNIIVRY</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1692.59</v>
+        <v>2168.95</v>
       </c>
       <c r="G32" t="n">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="M32" t="n">
-        <v>20311</v>
+        <v>19521</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2595,50 +2595,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0FTFVKTH6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>ULTIMUS128BLK</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t>Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C USB-A PD 65W PD 30W QC 30W Compatible</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2168.95</v>
+        <v>1518.1</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>46285</v>
+        <v>46279</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="M33" t="n">
-        <v>19521</v>
+        <v>16699</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2649,50 +2649,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0FTFVKTH6</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ULTIMUS128BLK</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C USB-A PD 65W PD 30W QC 30W Compatible</t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1518.1</v>
+        <v>2168.95</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>46279</v>
+        <v>46294</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>46283</v>
+        <v>46298</v>
       </c>
       <c r="M34" t="n">
-        <v>16699</v>
+        <v>13014</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2703,50 +2703,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0FTFVKTH6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>ULTIMUS128BLK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t>Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C USB-A PD 65W PD 30W QC 30W Compatible</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2168.95</v>
+        <v>1518.1</v>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I35" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46298</v>
+        <v>46290</v>
       </c>
       <c r="M35" t="n">
-        <v>13014</v>
+        <v>12145</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2765,27 +2765,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0FTFVKTH6</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ULTIMUS128BLK</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C USB-A PD 65W PD 30W QC 30W Compatible</t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1518.1</v>
+        <v>2168.95</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
         <v>46290</v>
       </c>
       <c r="M36" t="n">
-        <v>12145</v>
+        <v>10845</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2811,50 +2811,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0H2VFTQ1C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>WCNUMEN45PROWHT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2168.95</v>
+        <v>867.25</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="M37" t="n">
-        <v>10845</v>
+        <v>5204</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2865,50 +2865,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0H2VFTQ1C</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>WCNUMEN45PROWHT</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>867.25</v>
+        <v>1067.2</v>
       </c>
       <c r="G38" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>46279</v>
+        <v>46285</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="M38" t="n">
-        <v>5204</v>
+        <v>3202</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2927,30 +2927,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0GZVCYSXL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>WCNVS25CWHT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1067.2</v>
+        <v>433.36</v>
       </c>
       <c r="G39" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>46244</v>
@@ -2962,7 +2962,7 @@
         <v>46289</v>
       </c>
       <c r="M39" t="n">
-        <v>3202</v>
+        <v>867</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2973,113 +2973,59 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0GZVCYSXL</t>
+          <t>B0D3N594JW</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>WCNVS25CWHT</t>
+          <t>WRLREVELBLK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone</t>
+          <t>Stuffcool Revel Magnetic Wireless Qi2 Certified Charger- Charges iPhone 12/13/14/15/16 and Andr</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>433.36</v>
+        <v>762.2</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46285</v>
+        <v>46294</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>46289</v>
+        <v>46298</v>
       </c>
       <c r="M40" t="n">
-        <v>867</v>
+        <v>12195</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>5FPANY5G</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0D3N594JW</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>WRLREVELBLK</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Stuffcool Revel Magnetic Wireless Qi2 Certified Charger- Charges iPhone 12/13/14/15/16 and Andr</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>762.2</v>
-      </c>
-      <c r="G41" t="n">
-        <v>16</v>
-      </c>
-      <c r="H41" t="n">
-        <v>16</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>46298</v>
-      </c>
-      <c r="M41" t="n">
-        <v>12195</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
           <t>P5-No demand</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N41"/>
+  <autoFilter ref="A1:N40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3549,17 +3495,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0G4VHN9CZ</t>
+          <t>B0FWQYNB6P</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WCZENO65WWHT</t>
+          <t>WCJTPRO70WSIL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stuffcool Zeno 65W GaN Type C Fast Charger Retractable Cab</t>
+          <t>Stuffcool Jetset Pro Smallest 70W GaN International Travel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3573,7 +3519,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -3584,13 +3530,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>284</v>
+        <v>135</v>
       </c>
       <c r="K7" t="n">
-        <v>284</v>
+        <v>135</v>
       </c>
       <c r="L7" t="n">
-        <v>284</v>
+        <v>135</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3599,14 +3545,14 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1626.58</v>
+        <v>1789.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>461949</v>
+        <v>241554</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="S7" t="b">
@@ -3616,17 +3562,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0FWQYNB6P</t>
+          <t>B0FSRCKNCW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WCJTPRO70WSIL</t>
+          <t>PBNEMOSIL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stuffcool Jetset Pro Smallest 70W GaN International Travel</t>
+          <t>Stuffcool Nemo 10000mAh Compact Magnetic Wireless Charging</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3640,7 +3586,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -3651,13 +3597,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="K8" t="n">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3666,14 +3612,14 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1789.29</v>
+        <v>1524.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>241554</v>
+        <v>50319</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="S8" t="b">
@@ -3683,64 +3629,65 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B0FSRCKNCW</t>
+          <t>B0DMDZF5SV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PBNEMOSIL</t>
+          <t>PBGIGAGRY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stuffcool Nemo 10000mAh Compact Magnetic Wireless Charging</t>
+          <t>Stuffcool GIGA Smallest 65W 20000mAh Laptop Powerbank with</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P0b-New arrival, never sold</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>B-never sold (recent)</t>
+          <t>P1-Incumbent (running down)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>GIGA 20000</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>11.33333333333333</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.970588235294117</v>
       </c>
       <c r="J9" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>1218</v>
       </c>
       <c r="L9" t="n">
-        <v>33</v>
+        <v>91</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1127</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1524.81</v>
+        <v>2474.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>50319</v>
+        <v>225220</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>5FPANY5G, 5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S9" t="b">
@@ -3750,17 +3697,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0DMDZF5SV</t>
+          <t>B0DFZ3FK9F</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PBGIGAGRY</t>
+          <t>PBCLICK10TNM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stuffcool GIGA Smallest 65W 20000mAh Laptop Powerbank with</t>
+          <t xml:space="preserve">Stuffcool Click 10000mAh Slim Magnetic Wireless Powerbank </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3770,45 +3717,45 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GIGA 20000</t>
+          <t>Click 10000 magnetic</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="H10" t="n">
-        <v>11.33333333333333</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>6.970588235294117</v>
+        <v>12.55555555555556</v>
       </c>
       <c r="J10" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="K10" t="n">
-        <v>1218</v>
+        <v>760</v>
       </c>
       <c r="L10" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
         <v>15</v>
       </c>
       <c r="N10" t="n">
-        <v>1127</v>
+        <v>716</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2474.95</v>
+        <v>1185.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>225220</v>
+        <v>52177</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>5FPANY5G, 5OF8HBIC, 8Z6APQQC</t>
+          <t>5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S10" t="b">
@@ -3818,65 +3765,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0DFZ3FK9F</t>
+          <t>B0DZHKBBM1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PBCLICK10TNM</t>
+          <t>PBMAVERICKBLK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Click 10000mAh Slim Magnetic Wireless Powerbank </t>
+          <t>Stuffcool Maverick Mini 20,000mAh Powerbank with 20W Built</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P1-Incumbent (running down)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Click 10000 magnetic</t>
+          <t>P2-Critical</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>226</v>
+        <v>495</v>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="I11" t="n">
-        <v>12.55555555555556</v>
+        <v>11.88</v>
       </c>
       <c r="J11" t="n">
-        <v>44</v>
+        <v>963</v>
       </c>
       <c r="K11" t="n">
-        <v>760</v>
+        <v>606</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>606</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>26.4</v>
       </c>
       <c r="N11" t="n">
-        <v>716</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="P11" t="n">
-        <v>1185.85</v>
+        <v>1219.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>52177</v>
+        <v>739156</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>5OF8HBIC, 8Z6APQQC</t>
+          <t>5FPANY5G, 5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S11" t="b">
@@ -3886,17 +3828,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0DZHKBBM1</t>
+          <t>B0DFYZTJMC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PBMAVERICKBLK</t>
+          <t>PBROAM10WHT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stuffcool Maverick Mini 20,000mAh Powerbank with 20W Built</t>
+          <t xml:space="preserve">Stuffcool Roam 10000mAh Compact Powerbank with 20W Type C </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3905,41 +3847,41 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>495</v>
+        <v>53</v>
       </c>
       <c r="H12" t="n">
-        <v>41.66666666666666</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>11.88</v>
+        <v>14.45454545454546</v>
       </c>
       <c r="J12" t="n">
-        <v>963</v>
+        <v>75</v>
       </c>
       <c r="K12" t="n">
-        <v>606</v>
+        <v>123</v>
       </c>
       <c r="L12" t="n">
-        <v>606</v>
+        <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>26.4</v>
+        <v>34.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O12" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1219.73</v>
+        <v>889.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>739156</v>
+        <v>66693</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>5FPANY5G, 5OF8HBIC, 8Z6APQQC</t>
+          <t>5FPANY5G, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S12" t="b">
@@ -3949,17 +3891,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0DFYZTJMC</t>
+          <t>B0FT2VNW5H</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PBROAM10WHT</t>
+          <t>WCZENO30WWHT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Roam 10000mAh Compact Powerbank with 20W Type C </t>
+          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cab</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3968,41 +3910,41 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="H13" t="n">
-        <v>3.666666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="I13" t="n">
-        <v>14.45454545454546</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K13" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L13" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="N13" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>889.24</v>
+        <v>1084.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>66693</v>
+        <v>47705</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5FPANY5G, 8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="S13" t="b">
@@ -4012,17 +3954,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0FT2VNW5H</t>
+          <t>B0FSSCW7WZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WCZENO30WWHT</t>
+          <t>DUPLOBLK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cab</t>
+          <t xml:space="preserve">Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4031,41 +3973,41 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>1.666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>79</v>
+      </c>
+      <c r="L14" t="n">
+        <v>35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="N14" t="n">
         <v>44</v>
       </c>
-      <c r="K14" t="n">
-        <v>112</v>
-      </c>
-      <c r="L14" t="n">
-        <v>44</v>
-      </c>
-      <c r="M14" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="N14" t="n">
-        <v>68</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1084.2</v>
+        <v>698.6900000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>47705</v>
+        <v>24454</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ, 5OF8HBIC</t>
         </is>
       </c>
       <c r="S14" t="b">
@@ -4075,17 +4017,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0FSSCW7WZ</t>
+          <t>B0H6J3YQ1D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DUPLOBLK</t>
+          <t>WCNVS25CBLU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided </t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4094,41 +4036,41 @@
         </is>
       </c>
       <c r="G15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
         <v>12</v>
       </c>
-      <c r="H15" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="I15" t="n">
-        <v>9</v>
-      </c>
       <c r="J15" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K15" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="M15" t="n">
-        <v>35.2</v>
+        <v>21.5</v>
       </c>
       <c r="N15" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P15" t="n">
-        <v>698.6900000000001</v>
+        <v>433.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>24454</v>
+        <v>8234</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 5OF8HBIC</t>
+          <t>53SMQFHQ, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S15" t="b">
@@ -4138,17 +4080,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0H6J3YQ1D</t>
+          <t>B0H3ZPV2RJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WCNVS25CBLU</t>
+          <t>PBNIDOGRY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
+          <t>Stuffcool Nido 10000mAh Qi2.2 Certified Magsafe Powerbank,</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4157,42 +4099,37 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="J16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>21.5</v>
+        <v>10.5</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="P16" t="n">
-        <v>433.36</v>
+        <v>3092.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>8234</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>53SMQFHQ, 8Z6APQQC</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -4201,56 +4138,61 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0H3ZPV2RJ</t>
+          <t>B0FL2H8HZ6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PBNIDOGRY</t>
+          <t>PBGIGAMAXGRY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stuffcool Nido 10000mAh Qi2.2 Certified Magsafe Powerbank,</t>
+          <t>Stuffcool Giga Max Smallest 25000mAh 100W Power Bank, Buil</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P2-Critical</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>21</v>
+        <v>957</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>41.33333333333334</v>
       </c>
       <c r="I17" t="n">
-        <v>10.5</v>
+        <v>23.15322580645161</v>
       </c>
       <c r="J17" t="n">
-        <v>49</v>
+        <v>490</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="M17" t="n">
-        <v>10.5</v>
+        <v>35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="O17" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3092.6</v>
+        <v>3284.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1609209</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>5OF8HBIC, 8Z6APQQC</t>
+        </is>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -4259,17 +4201,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0FL2H8HZ6</t>
+          <t>B0D5JKBJTQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PBGIGAMAXGRY</t>
+          <t>PBMAJORULTRASIL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stuffcool Giga Max Smallest 25000mAh 100W Power Bank, Buil</t>
+          <t>Stuffcool Major Ultra 65W PD Super Fast USB Charging 20000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4278,41 +4220,41 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>957</v>
+        <v>367</v>
       </c>
       <c r="H18" t="n">
-        <v>41.33333333333334</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="I18" t="n">
-        <v>23.15322580645161</v>
+        <v>15.72857142857143</v>
       </c>
       <c r="J18" t="n">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="K18" t="n">
-        <v>2100</v>
+        <v>1076</v>
       </c>
       <c r="L18" t="n">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="M18" t="n">
         <v>35</v>
       </c>
       <c r="N18" t="n">
-        <v>1610</v>
+        <v>626</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3284.1</v>
+        <v>1601.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1609209</v>
+        <v>720495</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>5OF8HBIC, 8Z6APQQC</t>
+          <t>5FPANY5G, 5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S18" t="b">
@@ -4322,17 +4264,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0D5JKBJTQ</t>
+          <t>B0FHWN3M23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PBMAJORULTRASIL</t>
+          <t>PBODINSIL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stuffcool Major Ultra 65W PD Super Fast USB Charging 20000</t>
+          <t>Stuffcool Odin 10000mAh Qi2 MagSafe Powerbank with 15W Wir</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4341,41 +4283,41 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>367</v>
+        <v>242</v>
       </c>
       <c r="H19" t="n">
-        <v>23.33333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="I19" t="n">
-        <v>15.72857142857143</v>
+        <v>19.10526315789474</v>
       </c>
       <c r="J19" t="n">
-        <v>450</v>
+        <v>201</v>
       </c>
       <c r="K19" t="n">
-        <v>1076</v>
+        <v>748</v>
       </c>
       <c r="L19" t="n">
-        <v>450</v>
+        <v>201</v>
       </c>
       <c r="M19" t="n">
         <v>35</v>
       </c>
       <c r="N19" t="n">
-        <v>626</v>
+        <v>547</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1601.1</v>
+        <v>2382.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>720495</v>
+        <v>478866</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>5FPANY5G, 5OF8HBIC, 8Z6APQQC</t>
+          <t>5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S19" t="b">
@@ -4385,17 +4327,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0FHWN3M23</t>
+          <t>B0FY37VTSK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PBODINSIL</t>
+          <t>WCNMDPROSIL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stuffcool Odin 10000mAh Qi2 MagSafe Powerbank with 15W Wir</t>
+          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4404,41 +4346,41 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="H20" t="n">
-        <v>12.66666666666667</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="I20" t="n">
-        <v>19.10526315789474</v>
+        <v>24.85714285714285</v>
       </c>
       <c r="J20" t="n">
-        <v>201</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
-        <v>748</v>
+        <v>132</v>
       </c>
       <c r="L20" t="n">
-        <v>201</v>
+        <v>95</v>
       </c>
       <c r="M20" t="n">
         <v>35</v>
       </c>
       <c r="N20" t="n">
-        <v>547</v>
+        <v>37</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2382.42</v>
+        <v>3253.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>478866</v>
+        <v>309101</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>5OF8HBIC, 8Z6APQQC</t>
+          <t>53SMQFHQ, 5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S20" t="b">
@@ -4448,17 +4390,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0FY37VTSK</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WCNMDPROSIL</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TF</t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Typ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4467,41 +4409,41 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>232</v>
+        <v>92</v>
       </c>
       <c r="H21" t="n">
-        <v>9.333333333333334</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>24.85714285714285</v>
+        <v>21.23076923076923</v>
       </c>
       <c r="J21" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K21" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="L21" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="N21" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3253.69</v>
+        <v>2168.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>309101</v>
+        <v>130137</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 5OF8HBIC, 8Z6APQQC</t>
+          <t>53SMQFHQ, 5FPANY5G, 5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S21" t="b">
@@ -4511,17 +4453,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0GR982Q8W</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>WCNUMEN65WHT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Typ</t>
+          <t>Stuffcool Numen 65, Smallest 65W GaN Charger with Dual USB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4530,41 +4472,41 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>92</v>
+        <v>286</v>
       </c>
       <c r="H22" t="n">
-        <v>4.333333333333333</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>21.23076923076923</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="K22" t="n">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="L22" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="M22" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2168.95</v>
+        <v>1138.44</v>
       </c>
       <c r="Q22" t="n">
-        <v>130137</v>
+        <v>112706</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 5FPANY5G, 5OF8HBIC, 8Z6APQQC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="S22" t="b">
@@ -4574,17 +4516,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0GR982Q8W</t>
+          <t>B0FWSNDJ2V</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WCNUMEN65WHT</t>
+          <t>WCNMDIIWHT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Stuffcool Numen 65, Smallest 65W GaN Charger with Dual USB</t>
+          <t>Stuffcool Nomad II Smallest 100W GaN Charger PD PPS Suppor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4593,41 +4535,41 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>286</v>
+        <v>63</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>18.9</v>
       </c>
       <c r="J23" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="K23" t="n">
-        <v>285</v>
+        <v>32</v>
       </c>
       <c r="L23" t="n">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="M23" t="n">
-        <v>35</v>
+        <v>28.5</v>
       </c>
       <c r="N23" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P23" t="n">
-        <v>1138.44</v>
+        <v>2168.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>112706</v>
+        <v>69406</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="S23" t="b">
@@ -4637,17 +4579,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0FWSNDJ2V</t>
+          <t>B0H6Q2YQ9C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WCNMDIIWHT</t>
+          <t>PBOMNIPROSIL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Stuffcool Nomad II Smallest 100W GaN Charger PD PPS Suppor</t>
+          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4656,41 +4598,41 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H24" t="n">
-        <v>3.333333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>18.9</v>
+        <v>27.42857142857143</v>
       </c>
       <c r="J24" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L24" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="M24" t="n">
-        <v>28.5</v>
+        <v>35.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2168.95</v>
+        <v>3134.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>69406</v>
+        <v>56429</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5FPANY5G, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S24" t="b">
@@ -4700,17 +4642,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0H6Q2YQ9C</t>
+          <t>B0D8443PTW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PBOMNIPROSIL</t>
+          <t>QUADPROMAXBLK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 1</t>
+          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4719,41 +4661,41 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>64</v>
+        <v>360</v>
       </c>
       <c r="H25" t="n">
-        <v>2.333333333333333</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>27.42857142857143</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="K25" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L25" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="M25" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3134.97</v>
+        <v>508.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>56429</v>
+        <v>30483</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>5FPANY5G, 8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="S25" t="b">
@@ -4763,17 +4705,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0D8443PTW</t>
+          <t>B0FTFVKTH6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>QUADPROMAXBLK</t>
+          <t>ULTIMUS128BLK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240</t>
+          <t xml:space="preserve">Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4782,41 +4724,41 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>360</v>
+        <v>33</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>19.8</v>
       </c>
       <c r="J26" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K26" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="L26" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="M26" t="n">
-        <v>35</v>
+        <v>31.2</v>
       </c>
       <c r="N26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>508.05</v>
+        <v>1518.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>30483</v>
+        <v>28844</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>53SMQFHQ, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S26" t="b">
@@ -4826,17 +4768,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0FTFVKTH6</t>
+          <t>B0H5HYK4KZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ULTIMUS128BLK</t>
+          <t>PBOMNIIVRY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C </t>
+          <t>Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4845,41 +4787,41 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="H27" t="n">
-        <v>1.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="I27" t="n">
-        <v>19.8</v>
+        <v>30.375</v>
       </c>
       <c r="J27" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="L27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M27" t="n">
-        <v>31.2</v>
+        <v>34.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1518.1</v>
+        <v>1692.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>28844</v>
+        <v>20311</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 8Z6APQQC</t>
+          <t>5FPANY5G, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S27" t="b">
@@ -4889,17 +4831,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0H5HYK4KZ</t>
+          <t>B0H2VFTQ1C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PBOMNIIVRY</t>
+          <t>WCNUMEN45PROWHT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank</t>
+          <t>Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4908,41 +4850,41 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="H28" t="n">
-        <v>2.666666666666667</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>30.375</v>
+        <v>33.8</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1692.59</v>
+        <v>867.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>20311</v>
+        <v>5204</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>5FPANY5G, 8Z6APQQC</t>
+          <t>53SMQFHQ, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S28" t="b">
@@ -4952,17 +4894,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0H2VFTQ1C</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WCNUMEN45PROWHT</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD</t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4971,41 +4913,41 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>169</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I29" t="n">
-        <v>33.8</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N29" t="n">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>867.25</v>
+        <v>1067.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>5204</v>
+        <v>3202</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 8Z6APQQC</t>
+          <t>53SMQFHQ, 5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S29" t="b">
@@ -5015,17 +4957,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0GZVCYSXL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>WCNVS25CWHT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5034,41 +4976,41 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>15.81818181818182</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K30" t="n">
-        <v>217</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>36</v>
+        <v>16.4</v>
       </c>
       <c r="N30" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="P30" t="n">
-        <v>1067.2</v>
+        <v>433.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>3202</v>
+        <v>867</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 5OF8HBIC, 8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="S30" t="b">
@@ -5078,60 +5020,60 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0GZVCYSXL</t>
+          <t>B0DDTLRDJQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WCNVS25CWHT</t>
+          <t>PBLUCIDPLUSWHT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
+          <t>Stuffcool Lucid Plus 15W, 10000mAh Magnetic Wireless Power</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>58</v>
+        <v>307</v>
       </c>
       <c r="H31" t="n">
-        <v>3.666666666666667</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>15.81818181818182</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="J31" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>16.4</v>
+        <v>51.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O31" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>433.36</v>
+        <v>1779.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>867</v>
+        <v>0</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="S31" t="b">
@@ -5141,17 +5083,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0DDTLRDJQ</t>
+          <t>B0DJGVZSJS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PBLUCIDPLUSWHT</t>
+          <t>PRIMUSBLK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stuffcool Lucid Plus 15W, 10000mAh Magnetic Wireless Power</t>
+          <t>Stuffcool Primus USB 4 Type-C to Type-C Cable with 240W Po</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5160,41 +5102,41 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>307</v>
+        <v>1063</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="I32" t="n">
-        <v>51.16666666666666</v>
+        <v>60.16981132075471</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>26</v>
+        <v>1627</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>51.2</v>
+        <v>60.2</v>
       </c>
       <c r="N32" t="n">
-        <v>26</v>
+        <v>1627</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1779.07</v>
+        <v>465.68</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="S32" t="b">
@@ -5204,17 +5146,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0DJGVZSJS</t>
+          <t>B0FTFQ1RQT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PRIMUSBLK</t>
+          <t>WCSFC65WSIL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stuffcool Primus USB 4 Type-C to Type-C Cable with 240W Po</t>
+          <t>Stuffcool SoFar 65W Extension Wall Adapter with 2 Type-C &amp;</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5223,42 +5165,37 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1063</v>
+        <v>93</v>
       </c>
       <c r="H33" t="n">
-        <v>17.66666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="I33" t="n">
-        <v>60.16981132075471</v>
+        <v>55.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>1627</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>60.2</v>
+        <v>55.8</v>
       </c>
       <c r="N33" t="n">
-        <v>1627</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>465.68</v>
+        <v>1518.1</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>5OF8HBIC</t>
-        </is>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -5267,17 +5204,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0FTFQ1RQT</t>
+          <t>B0GN99CJ8F</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WCSFC65WSIL</t>
+          <t>WCZENO100WWHT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stuffcool SoFar 65W Extension Wall Adapter with 2 Type-C &amp;</t>
+          <t>Stuffcool Zeno 100W Desktop Charging Station, 65W Retracta</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5286,37 +5223,42 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="H34" t="n">
-        <v>1.666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I34" t="n">
-        <v>55.8</v>
+        <v>78</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>55.8</v>
+        <v>78</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1518.1</v>
+        <v>2168.95</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>5FPANY5G, 8Z6APQQC</t>
+        </is>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -5325,17 +5267,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0GN99CJ8F</t>
+          <t>B0GZBJRKSM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WCZENO100WWHT</t>
+          <t>PRIMUS1BLK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stuffcool Zeno 100W Desktop Charging Station, 65W Retracta</t>
+          <t>Stuffcool Primus USB 4 Type-C to Type-C Cable with 240W Po</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5344,41 +5286,41 @@
         </is>
       </c>
       <c r="G35" t="n">
+        <v>525</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>26</v>
       </c>
-      <c r="H35" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="I35" t="n">
-        <v>78</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>7</v>
-      </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>78</v>
+        <v>87.5</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2168.95</v>
+        <v>605.3</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>5FPANY5G, 8Z6APQQC</t>
+          <t>5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S35" t="b">
@@ -5388,17 +5330,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0GZBJRKSM</t>
+          <t>B0H54Z8RSJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PRIMUS1BLK</t>
+          <t>HKNVS25CCBLU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stuffcool Primus USB 4 Type-C to Type-C Cable with 240W Po</t>
+          <t xml:space="preserve">Stuffcool Novus 25W Super Fast GaN Charger with Type C to </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5407,41 +5349,41 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>525</v>
+        <v>68</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="I36" t="n">
-        <v>87.5</v>
+        <v>40.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>87.5</v>
+        <v>40.8</v>
       </c>
       <c r="N36" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>605.3</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>5OF8HBIC, 8Z6APQQC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="S36" t="b">
@@ -5451,12 +5393,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0H54Z8RSJ</t>
+          <t>B0H552PBFY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HKNVS25CCBLU</t>
+          <t>HKNVS25CCORG</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5470,28 +5412,28 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="H37" t="n">
         <v>1.666666666666667</v>
       </c>
       <c r="I37" t="n">
-        <v>40.8</v>
+        <v>58.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>40.8</v>
+        <v>58.2</v>
       </c>
       <c r="N37" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5504,7 +5446,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>53SMQFHQ, 5FPANY5G, 5OF8HBIC</t>
         </is>
       </c>
       <c r="S37" t="b">
@@ -5514,17 +5456,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0H552PBFY</t>
+          <t>B0H55MQK13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HKNVS25CCORG</t>
+          <t>WCNUMEN65CWHT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Novus 25W Super Fast GaN Charger with Type C to </t>
+          <t>Stuffcool Numen 65C, Smallest 65W GaN Charger with USB-C P</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5533,42 +5475,37 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="H38" t="n">
-        <v>1.666666666666667</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="I38" t="n">
-        <v>58.2</v>
+        <v>18.85714285714286</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K38" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>58.2</v>
+        <v>18.9</v>
       </c>
       <c r="N38" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P38" t="n">
-        <v>650.3099999999999</v>
+        <v>867.25</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>53SMQFHQ, 5FPANY5G, 5OF8HBIC</t>
-        </is>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -5577,12 +5514,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0H55MQK13</t>
+          <t>B0H55WWDH6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WCNUMEN65CWHT</t>
+          <t>HKNUMEN65CCCWHT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5596,37 +5533,42 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H39" t="n">
-        <v>4.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>18.85714285714286</v>
+        <v>87</v>
       </c>
       <c r="J39" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>18.9</v>
+        <v>87</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>867.25</v>
+        <v>1084.2</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8Z6APQQC</t>
+        </is>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -5635,17 +5577,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0H55WWDH6</t>
+          <t>B0H5J81W5D</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HKNUMEN65CCCWHT</t>
+          <t>PBOMNIGOBLK</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Stuffcool Numen 65C, Smallest 65W GaN Charger with USB-C P</t>
+          <t>Stuffcool Omni Go 3-in-1 10000mAh Smallest Magnetic Wirele</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5654,41 +5596,41 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="I40" t="n">
-        <v>87</v>
+        <v>45.1875</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>87</v>
+        <v>45.2</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1084.2</v>
+        <v>1441.75</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>53SMQFHQ, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S40" t="b">
@@ -5698,17 +5640,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0H5J81W5D</t>
+          <t>B0H6J36G1L</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PBOMNIGOBLK</t>
+          <t>HKNVS25CCWHT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Stuffcool Omni Go 3-in-1 10000mAh Smallest Magnetic Wirele</t>
+          <t xml:space="preserve">Stuffcool Novus 25W Super Fast GaN Charger with Type C to </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5717,41 +5659,41 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>241</v>
+        <v>109</v>
       </c>
       <c r="H41" t="n">
-        <v>5.333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I41" t="n">
-        <v>45.1875</v>
+        <v>327</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>45.2</v>
+        <v>327</v>
       </c>
       <c r="N41" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1441.75</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 8Z6APQQC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="S41" t="b">
@@ -5761,17 +5703,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0H6J36G1L</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>HKNVS25CCWHT</t>
+          <t>B0FWR73YG6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Novus 25W Super Fast GaN Charger with Type C to </t>
+          <t>Stuffcool Jetset Plus International Travel Adapter 30WGaNC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5780,42 +5717,31 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H42" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="I42" t="n">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="N42" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>650.3099999999999</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>53SMQFHQ</t>
-        </is>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -5824,12 +5750,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0FWR73YG6</t>
+          <t>B0G1T7S4NG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stuffcool Jetset Plus International Travel Adapter 30WGaNC</t>
+          <t>Stuffcool Nexi 3 in 1 Foldable Magnetic Wireless Charger Q</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5838,13 +5764,13 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I43" t="n">
-        <v>351</v>
+        <v>42</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5856,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>351</v>
+        <v>42</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5871,12 +5797,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0G1T7S4NG</t>
+          <t>B0G2XMZYGV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stuffcool Nexi 3 in 1 Foldable Magnetic Wireless Charger Q</t>
+          <t>Stuffcool Aura 10000mAh Magnetic Wireless Powerbank 15W Co</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5885,13 +5811,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5903,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5918,12 +5844,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0G2XMZYGV</t>
+          <t>B0H3VGY9GS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stuffcool Aura 10000mAh Magnetic Wireless Powerbank 15W Co</t>
+          <t>(ASIN B0H3VGY9GS)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5932,13 +5858,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>59</v>
+        <v>172</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I45" t="n">
-        <v>59</v>
+        <v>51.59999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5950,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>59</v>
+        <v>51.6</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5965,12 +5891,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0H3VGY9GS</t>
+          <t>B0H6J48B79</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>WCNVS25CORG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(ASIN B0H3VGY9GS)</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5979,13 +5910,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="H46" t="n">
-        <v>3.333333333333333</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="I46" t="n">
-        <v>51.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5997,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>51.6</v>
+        <v>67.5</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6012,50 +5943,60 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0H6J48B79</t>
+          <t>B0D3N594JW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WCNVS25CORG</t>
+          <t>WRLREVELBLK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
+          <t>Stuffcool Revel Magnetic Wireless Qi2 Certified Charger- C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>P5-No demand</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="I47" t="n">
-        <v>67.5</v>
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>67.5</v>
+        <v>16</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>762.2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>12195</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>5FPANY5G</t>
+        </is>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -6064,17 +6005,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0D3N594JW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>WRLREVELBLK</t>
+          <t>B00RWVNOF8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stuffcool Revel Magnetic Wireless Qi2 Certified Charger- C</t>
+          <t>(ASIN B00RWVNOF8)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6083,7 +6019,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -6097,27 +6033,16 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>762.2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>12195</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>5FPANY5G</t>
-        </is>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -6126,12 +6051,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B00RWVNOF8</t>
+          <t>B00TDKP72Y</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>(ASIN B00RWVNOF8)</t>
+          <t>(ASIN B00TDKP72Y)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6172,12 +6097,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B00TDKP72Y</t>
+          <t>B00U5PO54M</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>(ASIN B00TDKP72Y)</t>
+          <t>(ASIN B00U5PO54M)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6186,7 +6111,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -6218,12 +6143,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B00U5PO54M</t>
+          <t>B00UL9V8VU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>(ASIN B00U5PO54M)</t>
+          <t>(ASIN B00UL9V8VU)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6232,7 +6157,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -6264,12 +6189,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B00UL9V8VU</t>
+          <t>B00VK5CN18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>(ASIN B00UL9V8VU)</t>
+          <t>(ASIN B00VK5CN18)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6278,7 +6203,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -6310,12 +6235,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B00VK5CN18</t>
+          <t>B00WU81CGQ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>(ASIN B00VK5CN18)</t>
+          <t>(ASIN B00WU81CGQ)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6324,7 +6249,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -6356,12 +6281,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B00WU81CGQ</t>
+          <t>B0199YD7TS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>(ASIN B00WU81CGQ)</t>
+          <t>(ASIN B0199YD7TS)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6370,7 +6295,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -6402,12 +6327,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0199YD7TS</t>
+          <t>B01CJGOABM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(ASIN B0199YD7TS)</t>
+          <t>(ASIN B01CJGOABM)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6416,7 +6341,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -6448,12 +6373,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B01CJGOABM</t>
+          <t>B01DGLJJO2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>(ASIN B01CJGOABM)</t>
+          <t>(ASIN B01DGLJJO2)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6494,12 +6419,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B01DGLJJO2</t>
+          <t>B01LY66ZJR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>(ASIN B01DGLJJO2)</t>
+          <t>(ASIN B01LY66ZJR)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6540,12 +6465,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B01LY66ZJR</t>
+          <t>B01M3RFH5Q</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(ASIN B01LY66ZJR)</t>
+          <t>(ASIN B01M3RFH5Q)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6554,7 +6479,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -6586,12 +6511,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B01M3RFH5Q</t>
+          <t>B01M7S6ZRN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>(ASIN B01M3RFH5Q)</t>
+          <t>(ASIN B01M7S6ZRN)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6600,7 +6525,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -6632,12 +6557,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B01M7S6ZRN</t>
+          <t>B01MEGCXVC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>(ASIN B01M7S6ZRN)</t>
+          <t>(ASIN B01MEGCXVC)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6678,12 +6603,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B01MEGCXVC</t>
+          <t>B01MYTIMV2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>(ASIN B01MEGCXVC)</t>
+          <t>(ASIN B01MYTIMV2)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6724,12 +6649,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B01MYTIMV2</t>
+          <t>B01MZZ2VN3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>(ASIN B01MYTIMV2)</t>
+          <t>(ASIN B01MZZ2VN3)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6770,12 +6695,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B01MZZ2VN3</t>
+          <t>B01N2AVRCL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>(ASIN B01MZZ2VN3)</t>
+          <t>(ASIN B01N2AVRCL)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6816,12 +6741,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B01N2AVRCL</t>
+          <t>B0711C14G9</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>(ASIN B01N2AVRCL)</t>
+          <t>(ASIN B0711C14G9)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6862,12 +6787,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0711C14G9</t>
+          <t>B0713XNYS5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>(ASIN B0711C14G9)</t>
+          <t>(ASIN B0713XNYS5)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6876,7 +6801,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -6908,12 +6833,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0713XNYS5</t>
+          <t>B071NMG26X</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>(ASIN B0713XNYS5)</t>
+          <t>(ASIN B071NMG26X)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6922,7 +6847,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -6954,12 +6879,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B071NMG26X</t>
+          <t>B072L85KM1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>(ASIN B071NMG26X)</t>
+          <t>(ASIN B072L85KM1)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6968,7 +6893,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -7000,12 +6925,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B072L85KM1</t>
+          <t>B0733388FL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>(ASIN B072L85KM1)</t>
+          <t>(ASIN B0733388FL)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7014,7 +6939,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -7046,12 +6971,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0733388FL</t>
+          <t>B073FJCK38</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>(ASIN B0733388FL)</t>
+          <t>(ASIN B073FJCK38)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7060,7 +6985,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -7092,12 +7017,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B073FJCK38</t>
+          <t>B073FN9X73</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>(ASIN B073FJCK38)</t>
+          <t>(ASIN B073FN9X73)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7106,7 +7031,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -7138,12 +7063,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B073FN9X73</t>
+          <t>B075XNX87P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(ASIN B073FN9X73)</t>
+          <t>(ASIN B075XNX87P)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7152,7 +7077,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -7184,12 +7109,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B075XNX87P</t>
+          <t>B075XPWWQN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>(ASIN B075XNX87P)</t>
+          <t>(ASIN B075XPWWQN)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7230,12 +7155,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B075XPWWQN</t>
+          <t>B075ZQ6VLR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>(ASIN B075XPWWQN)</t>
+          <t>(ASIN B075ZQ6VLR)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7276,12 +7201,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B075ZQ6VLR</t>
+          <t>B075ZRPJRX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>(ASIN B075ZQ6VLR)</t>
+          <t>(ASIN B075ZRPJRX)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7290,7 +7215,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -7322,12 +7247,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B075ZRPJRX</t>
+          <t>B075ZRQSY2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(ASIN B075ZRPJRX)</t>
+          <t>(ASIN B075ZRQSY2)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7336,7 +7261,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -7368,12 +7293,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B075ZRQSY2</t>
+          <t>B07688F2WJ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(ASIN B075ZRQSY2)</t>
+          <t>(ASIN B07688F2WJ)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7414,12 +7339,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B07688F2WJ</t>
+          <t>B0768B9KHH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>(ASIN B07688F2WJ)</t>
+          <t>(ASIN B0768B9KHH)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7460,12 +7385,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0768B9KHH</t>
+          <t>B0768BGH4Q</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>(ASIN B0768B9KHH)</t>
+          <t>(ASIN B0768BGH4Q)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7506,12 +7431,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0768BGH4Q</t>
+          <t>B076BN3DT4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>(ASIN B0768BGH4Q)</t>
+          <t>(ASIN B076BN3DT4)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7552,12 +7477,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B076BN3DT4</t>
+          <t>B076X29CMV</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>(ASIN B076BN3DT4)</t>
+          <t>(ASIN B076X29CMV)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7598,12 +7523,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B076X29CMV</t>
+          <t>B0772MBFVT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>(ASIN B076X29CMV)</t>
+          <t>(ASIN B0772MBFVT)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7612,7 +7537,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -7644,12 +7569,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0772MBFVT</t>
+          <t>B0772QD768</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>(ASIN B0772MBFVT)</t>
+          <t>(ASIN B0772QD768)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7658,7 +7583,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -7690,12 +7615,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0772QD768</t>
+          <t>B078T666DS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>(ASIN B0772QD768)</t>
+          <t>(ASIN B078T666DS)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7736,12 +7661,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B078T666DS</t>
+          <t>B07BTD6VB7</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>(ASIN B078T666DS)</t>
+          <t>(ASIN B07BTD6VB7)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7782,12 +7707,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B07BTD6VB7</t>
+          <t>B07F9TK793</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>(ASIN B07BTD6VB7)</t>
+          <t>(ASIN B07F9TK793)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7828,12 +7753,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B07F9TK793</t>
+          <t>B08P5MFNRF</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>(ASIN B07F9TK793)</t>
+          <t>(ASIN B08P5MFNRF)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7874,12 +7799,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B08P5MFNRF</t>
+          <t>B0C2YR4MV6</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>(ASIN B08P5MFNRF)</t>
+          <t>(ASIN B0C2YR4MV6)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7920,12 +7845,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0C2YR4MV6</t>
+          <t>B0CF9Q7K51</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>(ASIN B0C2YR4MV6)</t>
+          <t>(ASIN B0CF9Q7K51)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7934,7 +7859,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -7966,12 +7891,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0CF9Q7K51</t>
+          <t>B0CVQD3KTB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>(ASIN B0CF9Q7K51)</t>
+          <t>(ASIN B0CVQD3KTB)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7980,7 +7905,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -8012,12 +7937,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0CVQD3KTB</t>
+          <t>B0DMVNDLHD</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>(ASIN B0CVQD3KTB)</t>
+          <t>(ASIN B0DMVNDLHD)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8026,7 +7951,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -8058,12 +7983,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0DMVNDLHD</t>
+          <t>B0FJ1HPZMY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>(ASIN B0DMVNDLHD)</t>
+          <t>(ASIN B0FJ1HPZMY)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8072,7 +7997,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -8104,12 +8029,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0FJ1HPZMY</t>
+          <t>B0GR8Z45XW</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>(ASIN B0FJ1HPZMY)</t>
+          <t>(ASIN B0GR8Z45XW)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8118,7 +8043,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -8150,12 +8075,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0GR8Z45XW</t>
+          <t>B0H1J18TTW</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>(ASIN B0GR8Z45XW)</t>
+          <t>(ASIN B0H1J18TTW)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8164,7 +8089,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -8196,12 +8121,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0H1J18TTW</t>
+          <t>B0H45M6MX5</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>(ASIN B0H1J18TTW)</t>
+          <t>(ASIN B0H45M6MX5)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8210,7 +8135,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -8242,21 +8167,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0H45M6MX5</t>
+          <t>B0BXXMZLDY</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PBSP85WBLK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>(ASIN B0H45M6MX5)</t>
+          <t>Stuffcool Super Power 85W 20000mAh Powerbank Compatible to</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>P5-No demand</t>
+          <t>X-EOL (not in Tally FY26-27)</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -8270,35 +8200,46 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>2960.17</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>5FPANY5G</t>
+        </is>
+      </c>
       <c r="S95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0BXXMZLDY</t>
+          <t>B0C3GT42X5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PBSP85WBLK</t>
+          <t>WCNOVA65WWHT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stuffcool Super Power 85W 20000mAh Powerbank Compatible to</t>
+          <t>Stuffcool Nova 65W Gan Charger Made in India 3 Ports Suppo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8307,7 +8248,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -8321,27 +8262,22 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2960.17</v>
+        <v>1270.68</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>5FPANY5G</t>
-        </is>
       </c>
       <c r="S96" t="b">
         <v>1</v>
@@ -8350,17 +8286,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0C3GT42X5</t>
+          <t>B0CCJ8BX6C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WCNOVA65WWHT</t>
+          <t>PBCLICKGRY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Stuffcool Nova 65W Gan Charger Made in India 3 Ports Suppo</t>
+          <t>Stuffcool Click 5000mAh Made in India Magnetic Wireless Po</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8369,7 +8305,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -8383,22 +8319,27 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>1270.68</v>
+        <v>1185.85</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>6WAHMIEG</t>
+        </is>
       </c>
       <c r="S97" t="b">
         <v>1</v>
@@ -8407,17 +8348,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0CCJ8BX6C</t>
+          <t>B0CMTDGZSP</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PBCLICKGRY</t>
+          <t>WCNV20WHT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Stuffcool Click 5000mAh Made in India Magnetic Wireless Po</t>
+          <t xml:space="preserve">Stuffcool Nuevo PD20W Made in India Smallest Wall Charger </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8426,7 +8367,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -8440,27 +8381,22 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>1185.85</v>
+        <v>304.58</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>6WAHMIEG</t>
-        </is>
       </c>
       <c r="S98" t="b">
         <v>1</v>
@@ -8469,17 +8405,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0CMTDGZSP</t>
+          <t>B0DB1MXGD4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WCNV20WHT</t>
+          <t>PBCLICKMAXWHT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Nuevo PD20W Made in India Smallest Wall Charger </t>
+          <t>Stuffcool Click Max 10000mAh Powerbank with Built-in PD20W</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8488,7 +8424,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -8502,22 +8438,27 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>304.58</v>
+        <v>1363.81</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>8Z6APQQC</t>
+        </is>
       </c>
       <c r="S99" t="b">
         <v>1</v>
@@ -8526,17 +8467,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0DB1MXGD4</t>
+          <t>B0DMVN35V5</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PBCLICKMAXWHT</t>
+          <t>RMSIP16PLBLK</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stuffcool Click Max 10000mAh Powerbank with Built-in PD20W</t>
+          <t>Stuffcool Rims Silicone case for iPhone 16 Plus, Magsafe E</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8559,26 +8500,26 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1363.81</v>
+        <v>863.9</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="S100" t="b">
@@ -8588,17 +8529,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0DMVN35V5</t>
+          <t>B0DSFKRMDM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RMSIP16PLBLK</t>
+          <t>QUADPRO2BLK</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Stuffcool Rims Silicone case for iPhone 16 Plus, Magsafe E</t>
+          <t>Stuffcool Quad Pro Black 4 in 1 Metal Braided Cable 1.5m 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8607,7 +8548,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -8621,26 +8562,26 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>863.9</v>
+        <v>380.93</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="S101" t="b">
@@ -8650,17 +8591,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0DSFKRMDM</t>
+          <t>B0FCYLK8C2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>QUADPRO2BLK</t>
+          <t>PBCLICKTRIOIVRY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro Black 4 in 1 Metal Braided Cable 1.5m 1</t>
+          <t xml:space="preserve">Stuffcool Click Trio 10000mAh Magnetic Wireless Powerbank </t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8668,8 +8609,13 @@
           <t>X-EOL (not in Tally FY26-27)</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>B-never sold (recent)</t>
+        </is>
+      </c>
       <c r="G102" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -8683,26 +8629,26 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>380.93</v>
+        <v>1692.59</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S102" t="b">
@@ -8712,64 +8658,60 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0FCYLK8C2</t>
+          <t>B0C1H6N3FX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PBCLICKTRIOIVRY</t>
+          <t>QUADPROBLK</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Click Trio 10000mAh Magnetic Wireless Powerbank </t>
+          <t>Stuffcool Quad Pro 4 in 1 Metal Flat Braided Indestructibl</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>X-EOL (not in Tally FY26-27)</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>B-never sold (recent)</t>
+          <t>X-No supply</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I103" t="n">
+        <v>195</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>56</v>
+        <v>912</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
       </c>
+      <c r="M103" t="n">
+        <v>195</v>
+      </c>
       <c r="N103" t="n">
-        <v>56</v>
+        <v>912</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>1692.59</v>
+        <v>355.42</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>5OF8HBIC, 8Z6APQQC</t>
+          <t>5FPANY5G, 5OF8HBIC</t>
         </is>
       </c>
       <c r="S103" t="b">
@@ -8779,17 +8721,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0C1H6N3FX</t>
+          <t>B0DFZ1KDPL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>QUADPROBLK</t>
+          <t>PBCLICK20TNM</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro 4 in 1 Metal Flat Braided Indestructibl</t>
+          <t>Stuffcool Click 20000mAh Magnetic Wireless Powerbank Natur</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8798,41 +8740,41 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="H104" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I104" t="n">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>912</v>
+        <v>367</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="N104" t="n">
-        <v>912</v>
+        <v>367</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>355.42</v>
+        <v>2075.68</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>5FPANY5G, 5OF8HBIC</t>
+          <t>53SMQFHQ, 5FPANY5G, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S104" t="b">
@@ -8842,17 +8784,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0DFZ1KDPL</t>
+          <t>B0G4VHN9CZ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PBCLICK20TNM</t>
+          <t>WCZENO65WWHT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Stuffcool Click 20000mAh Magnetic Wireless Powerbank Natur</t>
+          <t>Stuffcool Zeno 65W GaN Type C Fast Charger Retractable Cab</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8860,42 +8802,46 @@
           <t>X-No supply</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>B-never sold (recent)</t>
+        </is>
+      </c>
       <c r="G105" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="I105" t="n">
-        <v>78</v>
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>367</v>
+        <v>284</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
-      <c r="M105" t="n">
-        <v>78</v>
-      </c>
       <c r="N105" t="n">
-        <v>367</v>
+        <v>284</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2075.68</v>
+        <v>1626.58</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 5FPANY5G, 8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="S105" t="b">
@@ -9407,7 +9353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9969,97 +9915,97 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
+          <t>X-No supply</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0D5JKBJTQ</t>
+          <t>B0G4VHN9CZ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PBMAJORULTRASIL</t>
+          <t>WCZENO65WWHT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuffcool Major Ultra 65W PD Super Fast USB Charging 20000Mah Laptop Powerbank Supports Super F</t>
+          <t xml:space="preserve">Stuffcool Zeno 65W GaN Type C Fast Charger Retractable Cable 68cm PD PPS iPhone Pixel Supports </t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="J12" t="n">
-        <v>1601.1</v>
+        <v>1626.58</v>
       </c>
       <c r="K12" t="n">
-        <v>376258</v>
+        <v>461949</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X-No supply</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0DFZ1KDPL</t>
+          <t>B0D5JKBJTQ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PBCLICK20TNM</t>
+          <t>PBMAJORULTRASIL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuffcool Click 20000mAh Magnetic Wireless Powerbank Natural Titanium Finish Perfect for iPhone</t>
+          <t>Stuffcool Major Ultra 65W PD Super Fast USB Charging 20000Mah Laptop Powerbank Supports Super F</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>117</v>
+        <v>235</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>117</v>
+        <v>235</v>
       </c>
       <c r="J13" t="n">
-        <v>2075.68</v>
+        <v>1601.1</v>
       </c>
       <c r="K13" t="n">
-        <v>242855</v>
+        <v>376258</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="14">
@@ -10070,92 +10016,92 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0C1H6N3FX</t>
+          <t>B0DFZ1KDPL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>QUADPROBLK</t>
+          <t>PBCLICK20TNM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro 4 in 1 Metal Flat Braided Indestructible Cable 1.5m 60W with lightning to ty</t>
+          <t>Stuffcool Click 20000mAh Magnetic Wireless Powerbank Natural Titanium Finish Perfect for iPhone</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>670</v>
+        <v>117</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>670</v>
+        <v>117</v>
       </c>
       <c r="J14" t="n">
-        <v>355.42</v>
+        <v>2075.68</v>
       </c>
       <c r="K14" t="n">
-        <v>238131</v>
+        <v>242855</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
+          <t>X-No supply</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B0GR982Q8W</t>
+          <t>B0C1H6N3FX</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WCNUMEN65WHT</t>
+          <t>QUADPROBLK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuffcool Numen 65, Smallest 65W GaN Charger with Dual USB-C PD PPS &amp; USB-A, SFC 2.0 &amp; 3.0, AVS</t>
+          <t>Stuffcool Quad Pro 4 in 1 Metal Flat Braided Indestructible Cable 1.5m 60W with lightning to ty</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>285</v>
+        <v>670</v>
       </c>
       <c r="H15" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>186</v>
+        <v>670</v>
       </c>
       <c r="J15" t="n">
-        <v>1138.44</v>
+        <v>355.42</v>
       </c>
       <c r="K15" t="n">
-        <v>211750</v>
+        <v>238131</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="16">
@@ -10174,33 +10120,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0GR982Q8W</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>WCNUMEN65WHT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
+          <t>Stuffcool Numen 65, Smallest 65W GaN Charger with Dual USB-C PD PPS &amp; USB-A, SFC 2.0 &amp; 3.0, AVS</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>163</v>
+        <v>285</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="I16" t="n">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="J16" t="n">
-        <v>1067.2</v>
+        <v>1138.44</v>
       </c>
       <c r="K16" t="n">
-        <v>173954</v>
+        <v>211750</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>46290</v>
@@ -10222,33 +10168,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0H5HYK4KZ</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PBOMNIIVRY</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="H17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="J17" t="n">
-        <v>1692.59</v>
+        <v>1067.2</v>
       </c>
       <c r="K17" t="n">
-        <v>128637</v>
+        <v>173954</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>46290</v>
@@ -10270,33 +10216,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0FY37VTSK</t>
+          <t>B0H5HYK4KZ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WCNMDPROSIL</t>
+          <t>PBOMNIIVRY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TFT Display,Super Fast Charging 2.0 Cha</t>
+          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H18" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="J18" t="n">
-        <v>3253.69</v>
+        <v>1692.59</v>
       </c>
       <c r="K18" t="n">
-        <v>120387</v>
+        <v>128637</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>46290</v>
@@ -10305,241 +10251,241 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X-EOL (not in Tally FY26-27)</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0FCYLK8C2</t>
+          <t>B0FY37VTSK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PBCLICKTRIOIVRY</t>
+          <t>WCNMDPROSIL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Click Trio 10000mAh Magnetic Wireless Powerbank with Apple Watch Charging Module and </t>
+          <t>Stuffcool Nomad Pro 140W GaN Charger PD 3.1 AVS, Colour TFT Display,Super Fast Charging 2.0 Cha</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I19" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="J19" t="n">
-        <v>1692.59</v>
+        <v>3253.69</v>
       </c>
       <c r="K19" t="n">
-        <v>93092</v>
+        <v>120387</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X-No supply</t>
+          <t>X-EOL (not in Tally FY26-27)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0C1H6N3FX</t>
+          <t>B0FCYLK8C2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>QUADPROBLK</t>
+          <t>PBCLICKTRIOIVRY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro 4 in 1 Metal Flat Braided Indestructible Cable 1.5m 60W with lightning to ty</t>
+          <t xml:space="preserve">Stuffcool Click Trio 10000mAh Magnetic Wireless Powerbank with Apple Watch Charging Module and </t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>242</v>
+        <v>55</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>242</v>
+        <v>55</v>
       </c>
       <c r="J20" t="n">
-        <v>355.42</v>
+        <v>1692.59</v>
       </c>
       <c r="K20" t="n">
-        <v>86012</v>
+        <v>93092</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>X-No supply</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0H5J81W5D</t>
+          <t>B0C1H6N3FX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PBOMNIGOBLK</t>
+          <t>QUADPROBLK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuffcool Omni Go 3-in-1 10000mAh Smallest Magnetic Wireless Powerbank with Built-in Type-C Cab</t>
+          <t>Stuffcool Quad Pro 4 in 1 Metal Flat Braided Indestructible Cable 1.5m 60W with lightning to ty</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="J21" t="n">
-        <v>1441.75</v>
+        <v>355.42</v>
       </c>
       <c r="K21" t="n">
-        <v>79296</v>
+        <v>86012</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>46283</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P2-Critical</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B0FT2VNW5H</t>
+          <t>B0H5J81W5D</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WCZENO30WWHT</t>
+          <t>PBOMNIGOBLK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cable 75cm PD PPS iPhone Pixel Samsung S</t>
+          <t>Stuffcool Omni Go 3-in-1 10000mAh Smallest Magnetic Wireless Powerbank with Built-in Type-C Cab</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="H22" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="J22" t="n">
-        <v>1084.2</v>
+        <v>1441.75</v>
       </c>
       <c r="K22" t="n">
-        <v>73726</v>
+        <v>79296</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46298</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>P2-Critical</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0H5J81W5D</t>
+          <t>B0FT2VNW5H</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PBOMNIGOBLK</t>
+          <t>WCZENO30WWHT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuffcool Omni Go 3-in-1 10000mAh Smallest Magnetic Wireless Powerbank with Built-in Type-C Cab</t>
+          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cable 75cm PD PPS iPhone Pixel Samsung S</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I23" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="J23" t="n">
-        <v>1441.75</v>
+        <v>1084.2</v>
       </c>
       <c r="K23" t="n">
-        <v>61995</v>
+        <v>73726</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="24">
@@ -10558,33 +10504,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B0DDTLRDJQ</t>
+          <t>B0H5J81W5D</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PBLUCIDPLUSWHT</t>
+          <t>PBOMNIGOBLK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuffcool Lucid Plus 15W, 10000mAh Magnetic Wireless Powerbank with Stand for AirPods Pro, iPho</t>
+          <t>Stuffcool Omni Go 3-in-1 10000mAh Smallest Magnetic Wireless Powerbank with Built-in Type-C Cab</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="J24" t="n">
-        <v>1779.07</v>
+        <v>1441.75</v>
       </c>
       <c r="K24" t="n">
-        <v>46256</v>
+        <v>61995</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>46290</v>
@@ -10593,7 +10539,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P2-Critical</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10606,33 +10552,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B0DFYZTJMC</t>
+          <t>B0DDTLRDJQ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PBROAM10WHT</t>
+          <t>PBLUCIDPLUSWHT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Roam 10000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins </t>
+          <t>Stuffcool Lucid Plus 15W, 10000mAh Magnetic Wireless Powerbank with Stand for AirPods Pro, iPho</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="H25" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>889.24</v>
+        <v>1779.07</v>
       </c>
       <c r="K25" t="n">
-        <v>40905</v>
+        <v>46256</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>46290</v>
@@ -10641,55 +10587,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X-EOL (not in Tally FY26-27)</t>
+          <t>P2-Critical</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B0DSFKRMDM</t>
+          <t>B0DFYZTJMC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>QUADPRO2BLK</t>
+          <t>PBROAM10WHT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro Black 4 in 1 Metal Braided Cable 1.5m 100W Rugged E-Marker chip, case friend</t>
+          <t xml:space="preserve">Stuffcool Roam 10000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins </t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I26" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="J26" t="n">
-        <v>380.93</v>
+        <v>889.24</v>
       </c>
       <c r="K26" t="n">
-        <v>40379</v>
+        <v>40905</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
+          <t>X-EOL (not in Tally FY26-27)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10702,33 +10648,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0DSFKRMDM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>QUADPRO2BLK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
+          <t>Stuffcool Quad Pro Black 4 in 1 Metal Braided Cable 1.5m 100W Rugged E-Marker chip, case friend</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="J27" t="n">
-        <v>1067.2</v>
+        <v>380.93</v>
       </c>
       <c r="K27" t="n">
-        <v>33083</v>
+        <v>40379</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>46283</v>
@@ -10742,44 +10688,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J28" t="n">
-        <v>2168.95</v>
+        <v>1067.2</v>
       </c>
       <c r="K28" t="n">
-        <v>30365</v>
+        <v>33083</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>46298</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="29">
@@ -10790,50 +10736,50 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>1067.2</v>
+        <v>2168.95</v>
       </c>
       <c r="K29" t="n">
-        <v>21344</v>
+        <v>30365</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46289</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P2-Critical</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10846,33 +10792,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0FSSCW7WZ</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DUPLOBLK</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>698.6900000000001</v>
+        <v>1067.2</v>
       </c>
       <c r="K30" t="n">
-        <v>19563</v>
+        <v>21344</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>46289</v>
@@ -10881,97 +10827,97 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>P2-Critical</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0H6J36G1L</t>
+          <t>B0FSSCW7WZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HKNVS25CCWHT</t>
+          <t>DUPLOBLK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
+          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I31" t="n">
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>650.3099999999999</v>
+        <v>698.6900000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>18209</v>
+        <v>19563</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0H6Q2YQ9C</t>
+          <t>B0H6J36G1L</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PBOMNIPROSIL</t>
+          <t>HKNVS25CCWHT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 10000mAh with Apple Watch Charger, 35W</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H32" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>3134.97</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>15675</v>
+        <v>18209</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="33">
@@ -10982,332 +10928,332 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0H5HYK4KZ</t>
+          <t>B0H6Q2YQ9C</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PBOMNIIVRY</t>
+          <t>PBOMNIPROSIL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
+          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 10000mAh with Apple Watch Charger, 35W</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>1692.59</v>
+        <v>3134.97</v>
       </c>
       <c r="K33" t="n">
-        <v>15233</v>
+        <v>15675</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46298</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B0H552PBFY</t>
+          <t>B0H5HYK4KZ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HKNVS25CCORG</t>
+          <t>PBOMNIIVRY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
+          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J34" t="n">
-        <v>650.3099999999999</v>
+        <v>1692.59</v>
       </c>
       <c r="K34" t="n">
-        <v>13006</v>
+        <v>15233</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>46283</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X-EOL (not in Tally FY26-27)</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6WAHMIEG</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0CCJ8BX6C</t>
+          <t>B0H552PBFY</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PBCLICKGRY</t>
+          <t>HKNVS25CCORG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuffcool Click 5000mAh Made in India Magnetic Wireless Powerbank with 18W PD Fast Charing Type</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>1185.85</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>11858</v>
+        <v>13006</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P2-Critical</t>
+          <t>X-EOL (not in Tally FY26-27)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>6WAHMIEG</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0FSSCW7WZ</t>
+          <t>B0CCJ8BX6C</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DUPLOBLK</t>
+          <t>PBCLICKGRY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
+          <t>Stuffcool Click 5000mAh Made in India Magnetic Wireless Powerbank with 18W PD Fast Charing Type</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>698.6900000000001</v>
+        <v>1185.85</v>
       </c>
       <c r="K36" t="n">
-        <v>11179</v>
+        <v>11858</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>P2-Critical</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0GN99CJ8F</t>
+          <t>B0FSSCW7WZ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WCZENO100WWHT</t>
+          <t>DUPLOBLK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Zeno 100W Desktop Charging Station, 65W Retractable Type-C Cable, Dual 100W PD 3.0 &amp; </t>
+          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>2168.95</v>
+        <v>698.6900000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>10845</v>
+        <v>11179</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>46298</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0H2VFTQ1C</t>
+          <t>B0GN99CJ8F</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WCNUMEN45PROWHT</t>
+          <t>WCZENO100WWHT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
+          <t xml:space="preserve">Stuffcool Zeno 100W Desktop Charging Station, 65W Retractable Type-C Cable, Dual 100W PD 3.0 &amp; </t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>867.25</v>
+        <v>2168.95</v>
       </c>
       <c r="K38" t="n">
-        <v>8672</v>
+        <v>10845</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46283</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0GZBJRKSM</t>
+          <t>B0H2VFTQ1C</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PRIMUS1BLK</t>
+          <t>WCNUMEN45PROWHT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuffcool Primus USB 4 Type-C to Type-C Cable with 240W Power and 40Gbps Data with 8K Video Tra</t>
+          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>605.3</v>
+        <v>867.25</v>
       </c>
       <c r="K39" t="n">
-        <v>8474</v>
+        <v>8672</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="40">
@@ -11318,11 +11264,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -11340,22 +11286,22 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J40" t="n">
         <v>605.3</v>
       </c>
       <c r="K40" t="n">
-        <v>7264</v>
+        <v>8474</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="41">
@@ -11366,44 +11312,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0H552PBFY</t>
+          <t>B0GZBJRKSM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HKNVS25CCORG</t>
+          <t>PRIMUS1BLK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
+          <t>Stuffcool Primus USB 4 Type-C to Type-C Cable with 240W Power and 40Gbps Data with 8K Video Tra</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J41" t="n">
-        <v>650.3099999999999</v>
+        <v>605.3</v>
       </c>
       <c r="K41" t="n">
-        <v>6503</v>
+        <v>7264</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="42">
@@ -11414,20 +11360,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0H54Z8RSJ</t>
+          <t>B0H552PBFY</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HKNVS25CCBLU</t>
+          <t>HKNVS25CCORG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11451,132 +11397,132 @@
         <v>6503</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0D8443PTW</t>
+          <t>B0H54Z8RSJ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>QUADPROMAXBLK</t>
+          <t>HKNVS25CCBLU</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240W Rugged e-Marker chip gold plated co</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="H43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>508.05</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>6097</v>
+        <v>6503</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>X-EOL (not in Tally FY26-27)</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0BXXMZLDY</t>
+          <t>B0D8443PTW</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PBSP85WBLK</t>
+          <t>QUADPROMAXBLK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuffcool Super Power 85W 20000mAh Powerbank Compatible to Charge Macbooks, Laptops, iPads, Tab</t>
+          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240W Rugged e-Marker chip gold plated co</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J44" t="n">
-        <v>2960.17</v>
+        <v>508.05</v>
       </c>
       <c r="K44" t="n">
-        <v>5920</v>
+        <v>6097</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>X-EOL (not in Tally FY26-27)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0GN99CJ8F</t>
+          <t>B0BXXMZLDY</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>WCZENO100WWHT</t>
+          <t>PBSP85WBLK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Zeno 100W Desktop Charging Station, 65W Retractable Type-C Cable, Dual 100W PD 3.0 &amp; </t>
+          <t>Stuffcool Super Power 85W 20000mAh Powerbank Compatible to Charge Macbooks, Laptops, iPads, Tab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -11589,19 +11535,19 @@
         <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>2168.95</v>
+        <v>2960.17</v>
       </c>
       <c r="K45" t="n">
-        <v>4338</v>
+        <v>5920</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>P3-Top-up to 35d</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -11614,33 +11560,33 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0H2VFTQ1C</t>
+          <t>B0GN99CJ8F</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WCNUMEN45PROWHT</t>
+          <t>WCZENO100WWHT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
+          <t xml:space="preserve">Stuffcool Zeno 100W Desktop Charging Station, 65W Retractable Type-C Cable, Dual 100W PD 3.0 &amp; </t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>867.25</v>
+        <v>2168.95</v>
       </c>
       <c r="K46" t="n">
-        <v>3469</v>
+        <v>4338</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>46290</v>
@@ -11662,33 +11608,33 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0FL2H8HZ6</t>
+          <t>B0H2VFTQ1C</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PBGIGAMAXGRY</t>
+          <t>WCNUMEN45PROWHT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuffcool Giga Max Smallest 25000mAh 100W Power Bank, Built-in Type-C Cable, Charges MacBook Pr</t>
+          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>3284.1</v>
+        <v>867.25</v>
       </c>
       <c r="K47" t="n">
-        <v>3284</v>
+        <v>3469</v>
       </c>
       <c r="L47" s="3" t="n">
         <v>46290</v>
@@ -11702,25 +11648,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0H6Q2YQ9C</t>
+          <t>B0FL2H8HZ6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PBOMNIPROSIL</t>
+          <t>PBGIGAMAXGRY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 10000mAh with Apple Watch Charger, 35W</t>
+          <t>Stuffcool Giga Max Smallest 25000mAh 100W Power Bank, Built-in Type-C Cable, Charges MacBook Pr</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -11733,67 +11679,67 @@
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>3134.97</v>
+        <v>3284.1</v>
       </c>
       <c r="K48" t="n">
-        <v>3135</v>
+        <v>3284</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>46298</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P1-Incumbent (running down)</t>
+          <t>P3-Top-up to 35d</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0DFZ3FK9F</t>
+          <t>B0H6Q2YQ9C</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PBCLICK10TNM</t>
+          <t>PBOMNIPROSIL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuffcool Click 10000mAh Slim Magnetic Wireless Powerbank Natural Titanium Finish Perfect for i</t>
+          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 10000mAh with Apple Watch Charger, 35W</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1185.85</v>
+        <v>3134.97</v>
       </c>
       <c r="K49" t="n">
-        <v>2372</v>
+        <v>3135</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P4-Hold (at/over 35d)</t>
+          <t>P1-Incumbent (running down)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -11806,17 +11752,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0H55WWDH6</t>
+          <t>B0DFZ3FK9F</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HKNUMEN65CCCWHT</t>
+          <t>PBCLICK10TNM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuffcool Numen 65C, Smallest 65W GaN Charger with USB-C PD PPS, SFC 2.0/3.0, AVS Compatible, 1</t>
+          <t>Stuffcool Click 10000mAh Slim Magnetic Wireless Powerbank Natural Titanium Finish Perfect for i</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -11829,10 +11775,10 @@
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>1084.2</v>
+        <v>1185.85</v>
       </c>
       <c r="K50" t="n">
-        <v>2168</v>
+        <v>2372</v>
       </c>
       <c r="L50" s="3" t="n">
         <v>46290</v>
@@ -11841,103 +11787,103 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>X-No supply</t>
+          <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0DFZ1KDPL</t>
+          <t>B0H55WWDH6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PBCLICK20TNM</t>
+          <t>HKNUMEN65CCCWHT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuffcool Click 20000mAh Magnetic Wireless Powerbank Natural Titanium Finish Perfect for iPhone</t>
+          <t>Stuffcool Numen 65C, Smallest 65W GaN Charger with USB-C PD PPS, SFC 2.0/3.0, AVS Compatible, 1</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>2075.68</v>
+        <v>1084.2</v>
       </c>
       <c r="K51" t="n">
-        <v>2076</v>
+        <v>2168</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>P2-Critical</t>
+          <t>X-No supply</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0DFYZTJMC</t>
+          <t>B0DFZ1KDPL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PBROAM10WHT</t>
+          <t>PBCLICK20TNM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Roam 10000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins </t>
+          <t>Stuffcool Click 20000mAh Magnetic Wireless Powerbank Natural Titanium Finish Perfect for iPhone</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>889.24</v>
+        <v>2075.68</v>
       </c>
       <c r="K52" t="n">
-        <v>1778</v>
+        <v>2076</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>46298</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>X-EOL (not in Tally FY26-27)</t>
+          <t>P2-Critical</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -11950,17 +11896,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0DMVN35V5</t>
+          <t>B0DFYZTJMC</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RMSIP16PLBLK</t>
+          <t>PBROAM10WHT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuffcool Rims Silicone case for iPhone 16 Plus, Magsafe Enabled with a Raised Metallic Frame f</t>
+          <t xml:space="preserve">Stuffcool Roam 10000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins </t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11973,10 +11919,10 @@
         <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>863.9</v>
+        <v>889.24</v>
       </c>
       <c r="K53" t="n">
-        <v>1728</v>
+        <v>1778</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>46298</v>
@@ -11990,44 +11936,44 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0FCYLK8C2</t>
+          <t>B0DMVN35V5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PBCLICKTRIOIVRY</t>
+          <t>RMSIP16PLBLK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Click Trio 10000mAh Magnetic Wireless Powerbank with Apple Watch Charging Module and </t>
+          <t>Stuffcool Rims Silicone case for iPhone 16 Plus, Magsafe Enabled with a Raised Metallic Frame f</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>1692.59</v>
+        <v>863.9</v>
       </c>
       <c r="K54" t="n">
-        <v>1693</v>
+        <v>1728</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="55">
@@ -12046,17 +11992,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0DB1MXGD4</t>
+          <t>B0FCYLK8C2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PBCLICKMAXWHT</t>
+          <t>PBCLICKTRIOIVRY</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Click Max 10000mAh Powerbank with Built-in PD20W Type-C Cable to Fast Charge iPhones </t>
+          <t xml:space="preserve">Stuffcool Click Trio 10000mAh Magnetic Wireless Powerbank with Apple Watch Charging Module and </t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -12069,10 +12015,10 @@
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1363.81</v>
+        <v>1692.59</v>
       </c>
       <c r="K55" t="n">
-        <v>1364</v>
+        <v>1693</v>
       </c>
       <c r="L55" s="3" t="n">
         <v>46290</v>
@@ -12081,53 +12027,101 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>X-EOL (not in Tally FY26-27)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>8Z6APQQC</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>B0DB1MXGD4</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PBCLICKMAXWHT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stuffcool Click Max 10000mAh Powerbank with Built-in PD20W Type-C Cable to Fast Charge iPhones </t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1363.81</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>P4-Hold (at/over 35d)</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>5FPANY5G</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C57" s="3" t="n">
         <v>46265</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>B0H552PBFY</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>HKNVS25CCORG</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="G57" t="n">
         <v>2</v>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>2</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J57" t="n">
         <v>650.3099999999999</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K57" t="n">
         <v>1301</v>
       </c>
-      <c r="L56" s="3" t="n">
+      <c r="L57" s="3" t="n">
         <v>46298</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L56"/>
+  <autoFilter ref="A1:L57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/analysis/cocoblu-supply-2026-09-04/Cocoblu_Supply_Plan_v5_ISK3.xlsx
+++ b/analysis/cocoblu-supply-2026-09-04/Cocoblu_Supply_Plan_v5_ISK3.xlsx
@@ -17,7 +17,7 @@
     <sheet name="7_EOL - cancel these" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0_Summary'!$A$1:$B$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0_Summary'!$A$1:$B$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Dispatch by PO'!$A$1:$F$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_Dispatch lines'!$A$1:$N$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_SKU plan 35d'!$A$1:$S$105</definedName>
@@ -445,10 +445,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -467,53 +467,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Vendor code QZ73J / FC ISK3 only</t>
-        </is>
+          <t>&gt;&gt;&gt; RECOMMENDED SHIP NOW (units)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3845</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cover policy</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>35d cap on ESTABLISHED SKUs only</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>New arrivals</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>No cap - ship Amazon full ask (no DRR to cap on)</t>
-        </is>
-      </c>
-    </row>
+          <t>&gt;&gt;&gt; Recommended ship value (INR, vendor cost)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6833367</v>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sellable inventory at Cocoblu (3 Sep)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7815</v>
+          <t>-- how we get there --</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Open PO in scope (7 POs, ASN = 0)</t>
+          <t>Amazon open PO in scope (NOT a recommendation)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -523,135 +505,255 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RECOMMENDED SHIP NOW (units)</t>
+          <t xml:space="preserve">  less: unsupplyable (EOL or out of stock)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3845</v>
+        <v>-1740</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Recommended ship value (INR, vendor cost)</t>
+          <t xml:space="preserve">  less: held back - would breach 35d cover</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6833367</v>
+        <v>-7210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hold / cancel (units)</t>
+          <t xml:space="preserve">  = SHIP NOW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8950</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Units needed with no PO cover (ask Amazon)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SKUs shipped</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>29</v>
-      </c>
-    </row>
+          <t xml:space="preserve">  ship as % of open PO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Max DOH - established SKUs after ship</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>-- overstock check --</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>New arrival units (group A - new PO)</t>
+          <t>Established SKUs shipped</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1200</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>New arrival units (group B - never sold)</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>168</v>
+          <t>Max DOH of any established SKU after ship</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Excluded - no supply</t>
+          <t>Account cover now (days)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Click 20000, Quad Pro 1.5m 60W, Zeno 65W retractable</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Excluded - EOL (no Tally sale FY26-27)</t>
+          <t>Account cover after this shipment (days)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6 SKUs / 177u / Rs 156,034</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Excluded - other vendor code</t>
+          <t>Account cover IF we shipped the full open PO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PPAFS / 147u at HBA4, HKA2, HNR4, HPN6</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Inherited excess above 35d we ship nothing to</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>-- scope &amp; policy --</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vendor code QZ73J / FC ISK3 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cover policy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>35d cap on ESTABLISHED SKUs only</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>New arrivals</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>No cap - ship full ask (no DRR to cap on)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sellable inventory at Cocoblu (3 Sep)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7815</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Units needed with no PO cover (ask Amazon)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>New arrival units (group A - new PO)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>New arrival units (group B - never sold)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Excluded - no supply</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Click 20000, Quad Pro 1.5m 60W, Zeno 65W retractable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Excluded - EOL (no Tally sale FY26-27)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6 SKUs / 177u</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Excluded - other vendor code</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PPAFS / 147u at HBA4, HKA2, HNR4, HPN6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Excluded - EXPIRED PO</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>39VRVKCF / 1,105u - window closed 1 Sep, get it cancelled</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>39VRVKCF / 1,105u - window closed 1 Sep</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B18"/>
+  <autoFilter ref="A1:B31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
